--- a/documentation/4_ethics_and_licensing/SBOM.xlsx
+++ b/documentation/4_ethics_and_licensing/SBOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eaca\com2020\docs\3_ethics_and_licensing\software_and_data_inventory\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljmp1\IdeaProjects\com2020\documentation\4_ethics_and_licensing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1255DB20-A82C-4829-A58C-E4F4A07EEBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F160576-1D95-4319-B58B-691EBE8EF30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{4AABBBD3-43E7-4B06-BF25-05781DA341C4}"/>
+    <workbookView xWindow="-23148" yWindow="13788" windowWidth="23256" windowHeight="13896" xr2:uid="{4AABBBD3-43E7-4B06-BF25-05781DA341C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
   <si>
     <t>Software Bill of Materials</t>
   </si>
@@ -164,15 +164,9 @@
     <t>requests</t>
   </si>
   <si>
-    <t>pytest</t>
-  </si>
-  <si>
     <t>2.32.5</t>
   </si>
   <si>
-    <t>9.0.2</t>
-  </si>
-  <si>
     <t>Apache 2.0</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>BSD</t>
   </si>
   <si>
-    <t>https://pypi.org/project/pytest/</t>
-  </si>
-  <si>
     <t>https://pypi.org/project/requests/</t>
   </si>
   <si>
@@ -243,13 +234,85 @@
   </si>
   <si>
     <t>The Apache Software Foundation https://www.apache.org/licenses/</t>
+  </si>
+  <si>
+    <t>javafx-controls</t>
+  </si>
+  <si>
+    <t>org.openjfx</t>
+  </si>
+  <si>
+    <t>21.0.1</t>
+  </si>
+  <si>
+    <t>GPL 2.0</t>
+  </si>
+  <si>
+    <t>javafx-maven-plugin</t>
+  </si>
+  <si>
+    <t>jacoco-maven-plugin</t>
+  </si>
+  <si>
+    <t>org.jacoco</t>
+  </si>
+  <si>
+    <t>0.0.8</t>
+  </si>
+  <si>
+    <t>0.8.14</t>
+  </si>
+  <si>
+    <t>BSD 3-Clause</t>
+  </si>
+  <si>
+    <t>https://github.com/openjdk/jfx/blob/master/LICENSE</t>
+  </si>
+  <si>
+    <t>https://github.com/openjfx/javafx-maven-plugin/blob/master/LICENSE</t>
+  </si>
+  <si>
+    <t>https://www.eclipse.org/legal/epl-2.0/</t>
+  </si>
+  <si>
+    <t>pdoc</t>
+  </si>
+  <si>
+    <t>16.0.0</t>
+  </si>
+  <si>
+    <t>https://github.com/pdoc3/pdoc/blob/master/LICENSE.txt</t>
+  </si>
+  <si>
+    <t>coverage</t>
+  </si>
+  <si>
+    <t>7.13.4</t>
+  </si>
+  <si>
+    <t>https://github.com/coveragepy/coveragepy/blob/main/LICENSE.txt</t>
+  </si>
+  <si>
+    <t>https://github.com/openjdk/</t>
+  </si>
+  <si>
+    <t>https://github.com/openjfx/</t>
+  </si>
+  <si>
+    <t>https://www.eclipse.org/legal/</t>
+  </si>
+  <si>
+    <t>https://github.com/pdoc3</t>
+  </si>
+  <si>
+    <t>https://github.com/coveragepy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +324,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -441,10 +512,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -455,6 +527,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -467,58 +566,37 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -852,59 +930,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A40349-3CAD-48C4-ACC5-4B7769909782}">
   <dimension ref="B1:I38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
-    <col min="3" max="3" width="21.81640625" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="44.36328125" customWidth="1"/>
-    <col min="9" max="9" width="32.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.796875" customWidth="1"/>
+    <col min="4" max="4" width="28.5" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" customWidth="1"/>
+    <col min="7" max="7" width="55.19921875" customWidth="1"/>
+    <col min="8" max="8" width="44.3984375" customWidth="1"/>
+    <col min="9" max="9" width="32.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="10" t="s">
+    <row r="1" spans="2:9" ht="12" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="3" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="22"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="2:9" ht="19.95" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16"/>
-    </row>
-    <row r="4" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+    </row>
+    <row r="5" spans="2:9" ht="19.95" customHeight="1" thickBot="1"/>
+    <row r="6" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="B6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="9"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="19.95" customHeight="1">
       <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
@@ -921,411 +997,516 @@
         <v>3</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="28" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="40.049999999999997" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="23" t="s">
+      <c r="F8" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="40.049999999999997" customHeight="1">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="23" t="s">
+      <c r="F9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="19" t="s">
+      <c r="H9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="40.049999999999997" customHeight="1">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="40.049999999999997" customHeight="1">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="23" t="s">
+      <c r="F11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H11" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="40.049999999999997" customHeight="1">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="40.049999999999997" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E13" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="23" t="s">
+      <c r="F13" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
+      <c r="H13" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="36.6" customHeight="1">
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="24" t="s">
+      <c r="F14" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-    </row>
-    <row r="15" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="14" t="s">
+      <c r="H14" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="35.4" customHeight="1">
+      <c r="B15" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="37.799999999999997" customHeight="1" thickBot="1">
+      <c r="B16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="19.95" customHeight="1" thickBot="1"/>
+    <row r="18" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="B18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="29" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B19" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C19" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="30" t="s">
+      <c r="D19" s="25"/>
+      <c r="E19" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F19" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="28" t="s">
+      <c r="G19" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="19.95" customHeight="1">
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="16" t="s">
+      <c r="C20" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="18" t="s">
-        <v>62</v>
+      <c r="H20" s="27" t="s">
+        <v>59</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" ht="19.95" customHeight="1">
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="35"/>
+      <c r="E22" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="26.55" customHeight="1">
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="16" t="s">
+      <c r="D24" s="35"/>
+      <c r="E24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="18" t="s">
+      <c r="G24" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="B26" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="19.95" customHeight="1" thickBot="1"/>
+    <row r="28" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="B28" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
+    </row>
+    <row r="29" spans="2:9" ht="19.95" customHeight="1">
+      <c r="B29" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="19.95" customHeight="1" thickBot="1">
+      <c r="B30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="22"/>
-    </row>
-    <row r="25" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
+    </row>
+    <row r="31" spans="2:9" ht="19.95" customHeight="1"/>
+    <row r="32" spans="2:9" ht="19.95" customHeight="1"/>
+    <row r="33" ht="19.95" customHeight="1"/>
+    <row r="34" ht="19.95" customHeight="1"/>
+    <row r="35" ht="19.95" customHeight="1"/>
+    <row r="36" ht="19.95" customHeight="1"/>
+    <row r="37" ht="19.95" customHeight="1"/>
+    <row r="38" ht="19.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C25:D25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G10" r:id="rId1" xr:uid="{0E0DF48C-681E-45A9-8FA5-834BE2D531A1}"/>
+    <hyperlink ref="G15" r:id="rId2" xr:uid="{D21CE111-F4D6-48F3-A6E7-4759D72D94FD}"/>
+    <hyperlink ref="G25" r:id="rId3" xr:uid="{CAE30EDE-2F02-4686-92C5-E2A28B8245D5}"/>
+    <hyperlink ref="G26" r:id="rId4" xr:uid="{05BABC26-AFCF-4912-92AE-C779ACDD634F}"/>
+    <hyperlink ref="I10" r:id="rId5" xr:uid="{90590AF6-D8BB-48AD-9983-DA6745865032}"/>
+    <hyperlink ref="G16" r:id="rId6" xr:uid="{8A0FCE4B-B9A8-41A0-ABE7-0EC6A65187B1}"/>
+    <hyperlink ref="G11" r:id="rId7" xr:uid="{D5C6BBA0-36F8-48A2-B5D3-703B3205526D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>